--- a/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
+++ b/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
@@ -8,9 +8,7 @@
     <sheet state="visible" name="M2&amp;3 (C3)" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="M2&amp;3 (C4)" sheetId="4" r:id="rId8"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'M2&amp;3'!$A$1:$L$17</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
@@ -1887,7 +1885,6 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$A$1:$L$17"/>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699305555555556" right="0.699305555555556" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
+++ b/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
@@ -6715,7 +6715,7 @@
     <col customWidth="1" min="3" max="3" width="9.29"/>
     <col customWidth="1" min="4" max="4" width="14.71"/>
     <col customWidth="1" min="5" max="5" width="18.29"/>
-    <col customWidth="1" min="6" max="6" width="57.43"/>
+    <col customWidth="1" min="6" max="6" width="16.71"/>
     <col customWidth="1" min="7" max="26" width="7.86"/>
   </cols>
   <sheetData>

--- a/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
+++ b/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
@@ -167,7 +167,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -191,12 +191,6 @@
       <name val="Calibri"/>
     </font>
     <font/>
-    <font>
-      <i/>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -323,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -368,13 +362,7 @@
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1906,7 +1894,6 @@
     <col customWidth="1" min="5" max="5" width="18.29"/>
     <col customWidth="1" min="6" max="6" width="57.43"/>
     <col customWidth="1" min="7" max="16" width="7.86"/>
-    <col customWidth="1" min="17" max="19" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -2011,41 +1998,36 @@
       <c r="P4" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>1.0</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="24"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>
@@ -4478,7 +4460,6 @@
     <col customWidth="1" min="5" max="5" width="18.29"/>
     <col customWidth="1" min="6" max="6" width="57.43"/>
     <col customWidth="1" min="7" max="12" width="7.86"/>
-    <col customWidth="1" min="13" max="21" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -4511,7 +4492,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
       <c r="J2" s="13"/>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="23" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="15"/>
@@ -4559,49 +4540,32 @@
       <c r="L4" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M4" s="22"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>1.0</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="24"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>
@@ -6740,7 +6704,7 @@
       <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="24" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="11" t="s">
@@ -6763,7 +6727,7 @@
       <c r="V2" s="12"/>
       <c r="W2" s="12"/>
       <c r="X2" s="13"/>
-      <c r="Y2" s="25" t="s">
+      <c r="Y2" s="23" t="s">
         <v>19</v>
       </c>
       <c r="Z2" s="15"/>
@@ -6774,7 +6738,7 @@
       <c r="C3" s="16"/>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
-      <c r="F3" s="27"/>
+      <c r="F3" s="25"/>
       <c r="G3" s="11" t="s">
         <v>37</v>
       </c>
@@ -6883,44 +6847,44 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="23">
+      <c r="A5" s="22">
         <v>1.0</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="23"/>
-      <c r="Z5" s="23"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="22"/>
+      <c r="W5" s="22"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>

--- a/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
+++ b/HVNCLC/2025-2026/REPORT/REPORT_RM2&3.xlsx
@@ -3,13 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="M2&amp;3" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="M2&amp;3 (C2)" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="M2&amp;3 (C3)" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="M2&amp;3 (C4)" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="M2&amp;3" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="M2&amp;3 (C2)" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="M2&amp;3 (C3)" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="M2&amp;3 (C4)" sheetId="4" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'M2&amp;3'!$A$1:$L$17</definedName>
+  </definedNames>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="T80LszvfYWoz5XENLRw6V3M9sPBRvO3dGtyGEjneuE4="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -167,12 +174,22 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
@@ -183,14 +200,15 @@
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font/>
+    <font>
+      <i/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -202,20 +220,6 @@
   </fills>
   <borders count="13">
     <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -312,65 +316,74 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -393,10 +406,6 @@
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -638,256 +647,256 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="1">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -1873,6 +1882,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="$A$1:$L$17"/>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699305555555556" right="0.699305555555556" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1894,1740 +1904,1746 @@
     <col customWidth="1" min="5" max="5" width="18.29"/>
     <col customWidth="1" min="6" max="6" width="57.43"/>
     <col customWidth="1" min="7" max="16" width="7.86"/>
+    <col customWidth="1" min="17" max="19" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="14" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="15"/>
+      <c r="P2" s="12"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="11" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="17" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="17" t="s">
+      <c r="J3" s="10"/>
+      <c r="K3" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="11" t="s">
+      <c r="L3" s="10"/>
+      <c r="M3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="18"/>
-      <c r="P3" s="19"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="16"/>
     </row>
     <row r="4" ht="189.0" customHeight="1">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="N4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="18" t="s">
         <v>27</v>
       </c>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="22">
+      <c r="A5" s="20">
         <v>1.0</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="21"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="6"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="6"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="6"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="6"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="6"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="6"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="6"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="6"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="6"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="6"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="6"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="6"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="6"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="6"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="6"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="6"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="6"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="6"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="6"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="6"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="6"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="6"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="6"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="6"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="6"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="6"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="6"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="6"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="6"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="6"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="6"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="6"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="6"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="6"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="6"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="6"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="6"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="6"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="6"/>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="6"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="6"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="6"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="6"/>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="6"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="6"/>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="6"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="6"/>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="6"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="6"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="6"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="6"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="6"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="6"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="6"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="6"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="6"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="6"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="6"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="6"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="6"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="6"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="6"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="6"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="6"/>
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="6"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="6"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="6"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="6"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="6"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="6"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="6"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="6"/>
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="6"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="6"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="6"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="6"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="6"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="6"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="6"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="6"/>
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="6"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="6"/>
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="6"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="6"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="6"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="6"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="6"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="6"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="6"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="6"/>
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="6"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="6"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="6"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="6"/>
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="6"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="6"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="6"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="6"/>
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="6"/>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="6"/>
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="6"/>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="6"/>
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="6"/>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="6"/>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="6"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="6"/>
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="6"/>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="6"/>
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="6"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="6"/>
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="6"/>
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="6"/>
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="6"/>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="6"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="6"/>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="6"/>
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="6"/>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="6"/>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="6"/>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="6"/>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="6"/>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="6"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="6"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="6"/>
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="6"/>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="6"/>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="6"/>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="6"/>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="6"/>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="6"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="6"/>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="6"/>
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="6"/>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="6"/>
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="6"/>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="6"/>
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="6"/>
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="6"/>
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="6"/>
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="6"/>
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="6"/>
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="6"/>
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="6"/>
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="6"/>
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="6"/>
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="6"/>
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="6"/>
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="6"/>
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="6"/>
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="6"/>
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="6"/>
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="7"/>
-      <c r="F176" s="6"/>
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="6"/>
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="6"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="6"/>
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="6"/>
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="6"/>
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="6"/>
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="7"/>
-      <c r="F183" s="6"/>
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="6"/>
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="3"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="6"/>
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="3"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="6"/>
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
+      <c r="E186" s="4"/>
+      <c r="F186" s="3"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
-      <c r="E187" s="7"/>
-      <c r="F187" s="6"/>
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
+      <c r="E187" s="4"/>
+      <c r="F187" s="3"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
-      <c r="E188" s="7"/>
-      <c r="F188" s="6"/>
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
+      <c r="E188" s="4"/>
+      <c r="F188" s="3"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
-      <c r="E189" s="7"/>
-      <c r="F189" s="6"/>
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="3"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
-      <c r="E190" s="7"/>
-      <c r="F190" s="6"/>
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
+      <c r="E190" s="4"/>
+      <c r="F190" s="3"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
-      <c r="E191" s="7"/>
-      <c r="F191" s="6"/>
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="4"/>
+      <c r="F191" s="3"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
-      <c r="E192" s="7"/>
-      <c r="F192" s="6"/>
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="4"/>
+      <c r="F192" s="3"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
-      <c r="E193" s="7"/>
-      <c r="F193" s="6"/>
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
+      <c r="E193" s="4"/>
+      <c r="F193" s="3"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
-      <c r="E194" s="7"/>
-      <c r="F194" s="6"/>
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
+      <c r="E194" s="4"/>
+      <c r="F194" s="3"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
-      <c r="E195" s="7"/>
-      <c r="F195" s="6"/>
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="3"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-      <c r="E196" s="7"/>
-      <c r="F196" s="6"/>
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="3"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
-      <c r="E197" s="7"/>
-      <c r="F197" s="6"/>
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="4"/>
+      <c r="F197" s="3"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
-      <c r="E198" s="7"/>
-      <c r="F198" s="6"/>
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="3"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
-      <c r="E199" s="7"/>
-      <c r="F199" s="6"/>
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
+      <c r="E199" s="4"/>
+      <c r="F199" s="3"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
-      <c r="E200" s="7"/>
-      <c r="F200" s="6"/>
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
+      <c r="E200" s="4"/>
+      <c r="F200" s="3"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
-      <c r="E201" s="7"/>
-      <c r="F201" s="6"/>
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="3"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="6"/>
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="3"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="6"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+      <c r="E203" s="4"/>
+      <c r="F203" s="3"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="6"/>
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="4"/>
+      <c r="F204" s="3"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-      <c r="E205" s="7"/>
-      <c r="F205" s="6"/>
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="3"/>
     </row>
     <row r="206" ht="14.25" customHeight="1"/>
     <row r="207" ht="14.25" customHeight="1"/>
@@ -4460,1352 +4476,1370 @@
     <col customWidth="1" min="5" max="5" width="18.29"/>
     <col customWidth="1" min="6" max="6" width="57.43"/>
     <col customWidth="1" min="7" max="12" width="7.86"/>
+    <col customWidth="1" min="13" max="21" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="23" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="15"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="11" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="16"/>
     </row>
     <row r="4" ht="245.25" customHeight="1">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="21" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="18" t="s">
         <v>27</v>
       </c>
+      <c r="M4" s="19"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="22">
+      <c r="A5" s="20">
         <v>1.0</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="21"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="6"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="6"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="6"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="6"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="6"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="6"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="6"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="6"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="6"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="6"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="6"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="6"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="6"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="6"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="6"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="6"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="6"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="6"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="6"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="6"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="6"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="6"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="6"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="6"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="6"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="6"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="6"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="6"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="6"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="6"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="6"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="6"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="6"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="6"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="6"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="6"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="6"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="6"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="6"/>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="6"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="6"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="6"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="6"/>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="6"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="6"/>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="6"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="6"/>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="6"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="6"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="6"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="6"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="6"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="6"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="6"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="6"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="6"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="6"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="6"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="6"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="6"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="6"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="6"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="6"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="6"/>
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="6"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="6"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="6"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="6"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="6"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="6"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="6"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="6"/>
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="6"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="6"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="6"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="6"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="6"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="6"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="6"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="6"/>
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="6"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="6"/>
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="6"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="6"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="6"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="6"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="6"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="6"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="6"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="6"/>
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="6"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="6"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="6"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="6"/>
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="6"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="6"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="6"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="6"/>
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="6"/>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="6"/>
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="6"/>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="6"/>
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="6"/>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="6"/>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="6"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="6"/>
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="6"/>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="6"/>
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="6"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="6"/>
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="6"/>
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="6"/>
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="6"/>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="6"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="6"/>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="6"/>
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="6"/>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="6"/>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="6"/>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="6"/>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="6"/>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="6"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="6"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="6"/>
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="6"/>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="6"/>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="6"/>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="6"/>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="6"/>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="6"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="6"/>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="6"/>
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="6"/>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="6"/>
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="6"/>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="6"/>
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="3"/>
     </row>
     <row r="161" ht="14.25" customHeight="1"/>
     <row r="162" ht="14.25" customHeight="1"/>
@@ -6679,1644 +6713,1644 @@
     <col customWidth="1" min="3" max="3" width="9.29"/>
     <col customWidth="1" min="4" max="4" width="14.71"/>
     <col customWidth="1" min="5" max="5" width="18.29"/>
-    <col customWidth="1" min="6" max="6" width="16.71"/>
+    <col customWidth="1" min="6" max="6" width="57.43"/>
     <col customWidth="1" min="7" max="26" width="7.86"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="23" t="s">
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="15"/>
+      <c r="Z2" s="12"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="11" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="11" t="s">
+      <c r="H3" s="10"/>
+      <c r="I3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="11" t="s">
+      <c r="J3" s="10"/>
+      <c r="K3" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="11" t="s">
+      <c r="L3" s="10"/>
+      <c r="M3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="13"/>
-      <c r="O3" s="11" t="s">
+      <c r="N3" s="10"/>
+      <c r="O3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="11" t="s">
+      <c r="P3" s="10"/>
+      <c r="Q3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="R3" s="13"/>
-      <c r="S3" s="11" t="s">
+      <c r="R3" s="10"/>
+      <c r="S3" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="T3" s="13"/>
-      <c r="U3" s="11" t="s">
+      <c r="T3" s="10"/>
+      <c r="U3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="V3" s="13"/>
-      <c r="W3" s="11" t="s">
+      <c r="V3" s="10"/>
+      <c r="W3" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="18"/>
-      <c r="Z3" s="19"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="16"/>
     </row>
     <row r="4" ht="213.0" customHeight="1">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="21" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="H4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="21" t="s">
+      <c r="N4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="21" t="s">
+      <c r="O4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="21" t="s">
+      <c r="Q4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="R4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="S4" s="21" t="s">
+      <c r="S4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="21" t="s">
+      <c r="T4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="U4" s="21" t="s">
+      <c r="U4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="21" t="s">
+      <c r="V4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="21" t="s">
+      <c r="W4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="X4" s="21" t="s">
+      <c r="X4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="Y4" s="21" t="s">
+      <c r="Y4" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="Z4" s="21" t="s">
+      <c r="Z4" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="22">
+      <c r="A5" s="20">
         <v>1.0</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="22"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="6"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="6"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="3"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="6"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="6"/>
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="6"/>
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="6"/>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="6"/>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="6"/>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="6"/>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="6"/>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="6"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="6"/>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="6"/>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="6"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="6"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="6"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="6"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="6"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="6"/>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="6"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="6"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="6"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="6"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="6"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="6"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="6"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="3"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="6"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="6"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="3"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="6"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="6"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="3"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="6"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="3"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="6"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="6"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="3"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="6"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="3"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="6"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="6"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="3"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="6"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="3"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="6"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="3"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="6"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="3"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="6"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="3"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="6"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="3"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="6"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="3"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="6"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="3"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="6"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="3"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="6"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="3"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="6"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="3"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="6"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="3"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="6"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="3"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="6"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="3"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="6"/>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="3"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="6"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="3"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="6"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="3"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="6"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="3"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="6"/>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="6"/>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="3"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="6"/>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="3"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="6"/>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="3"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="6"/>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="3"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="6"/>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="3"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="6"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="3"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="6"/>
+      <c r="A74" s="3"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="3"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="6"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="3"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="6"/>
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="3"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="6"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="3"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="6"/>
+      <c r="A78" s="3"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="3"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="6"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="3"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="6"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="3"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="6"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="3"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="6"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="3"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="6"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="3"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="6"/>
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="3"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="6"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="3"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="6"/>
+      <c r="A86" s="3"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="3"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="6"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="3"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="6"/>
+      <c r="A88" s="3"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="3"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="6"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="3"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="6"/>
+      <c r="A90" s="3"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="3"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="6"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="3"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="6"/>
+      <c r="A92" s="3"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="4"/>
+      <c r="F92" s="3"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="6"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="4"/>
+      <c r="F93" s="3"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="6"/>
+      <c r="A94" s="3"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="3"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="7"/>
-      <c r="F95" s="6"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="4"/>
+      <c r="F95" s="3"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="7"/>
-      <c r="F96" s="6"/>
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="3"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
-      <c r="E97" s="7"/>
-      <c r="F97" s="6"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="4"/>
+      <c r="F97" s="3"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
-      <c r="E98" s="7"/>
-      <c r="F98" s="6"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="3"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="6"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="3"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="7"/>
-      <c r="F100" s="6"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="3"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="6"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="3"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="6"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="3"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="7"/>
-      <c r="F103" s="6"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="3"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
-      <c r="E104" s="7"/>
-      <c r="F104" s="6"/>
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="3"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
-      <c r="E105" s="7"/>
-      <c r="F105" s="6"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="3"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="6"/>
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="3"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
-      <c r="E107" s="7"/>
-      <c r="F107" s="6"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="3"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
-      <c r="E108" s="7"/>
-      <c r="F108" s="6"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="3"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
-      <c r="E109" s="7"/>
-      <c r="F109" s="6"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="3"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="6"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="3"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="7"/>
-      <c r="F111" s="6"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="3"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="6"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="3"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
-      <c r="E113" s="7"/>
-      <c r="F113" s="6"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="3"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
-      <c r="E114" s="7"/>
-      <c r="F114" s="6"/>
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="3"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
-      <c r="E115" s="7"/>
-      <c r="F115" s="6"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="3"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
-      <c r="E116" s="7"/>
-      <c r="F116" s="6"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="3"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
-      <c r="E117" s="7"/>
-      <c r="F117" s="6"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="3"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="7"/>
-      <c r="F118" s="6"/>
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="4"/>
+      <c r="F118" s="3"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
-      <c r="E119" s="7"/>
-      <c r="F119" s="6"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="3"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="6"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="4"/>
+      <c r="F120" s="3"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
-      <c r="E121" s="7"/>
-      <c r="F121" s="6"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="4"/>
+      <c r="F121" s="3"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
-      <c r="E122" s="7"/>
-      <c r="F122" s="6"/>
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
+      <c r="E122" s="4"/>
+      <c r="F122" s="3"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
-      <c r="E123" s="7"/>
-      <c r="F123" s="6"/>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
+      <c r="E123" s="4"/>
+      <c r="F123" s="3"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="6"/>
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
+      <c r="E124" s="4"/>
+      <c r="F124" s="3"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="6"/>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
+      <c r="E125" s="4"/>
+      <c r="F125" s="3"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
-      <c r="E126" s="7"/>
-      <c r="F126" s="6"/>
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="3"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="6"/>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
+      <c r="E127" s="4"/>
+      <c r="F127" s="3"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="7"/>
-      <c r="F128" s="6"/>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
+      <c r="E128" s="4"/>
+      <c r="F128" s="3"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
-      <c r="E129" s="7"/>
-      <c r="F129" s="6"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="3"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="6"/>
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+      <c r="E130" s="4"/>
+      <c r="F130" s="3"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
-      <c r="E131" s="7"/>
-      <c r="F131" s="6"/>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="4"/>
+      <c r="F131" s="3"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="6"/>
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="4"/>
+      <c r="F132" s="3"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
-      <c r="E133" s="7"/>
-      <c r="F133" s="6"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="3"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
-      <c r="E134" s="7"/>
-      <c r="F134" s="6"/>
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="3"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
-      <c r="E135" s="7"/>
-      <c r="F135" s="6"/>
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="3"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="6"/>
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="4"/>
+      <c r="F136" s="3"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="6"/>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="4"/>
+      <c r="F137" s="3"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="6"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="4"/>
+      <c r="F138" s="3"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="6"/>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="3"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
-      <c r="E140" s="7"/>
-      <c r="F140" s="6"/>
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="4"/>
+      <c r="F140" s="3"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
-      <c r="E141" s="7"/>
-      <c r="F141" s="6"/>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="3"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="7"/>
-      <c r="F142" s="6"/>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="3"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
-      <c r="E143" s="7"/>
-      <c r="F143" s="6"/>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="4"/>
+      <c r="F143" s="3"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
-      <c r="E144" s="7"/>
-      <c r="F144" s="6"/>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="3"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
-      <c r="E145" s="7"/>
-      <c r="F145" s="6"/>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="4"/>
+      <c r="F145" s="3"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="6"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="3"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="6"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="3"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="6"/>
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="4"/>
+      <c r="F148" s="3"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
-      <c r="E149" s="7"/>
-      <c r="F149" s="6"/>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="3"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
-      <c r="E150" s="7"/>
-      <c r="F150" s="6"/>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="4"/>
+      <c r="F150" s="3"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="6"/>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="3"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
-      <c r="E152" s="7"/>
-      <c r="F152" s="6"/>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="4"/>
+      <c r="F152" s="3"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
-      <c r="E153" s="7"/>
-      <c r="F153" s="6"/>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="4"/>
+      <c r="F153" s="3"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
-      <c r="E154" s="7"/>
-      <c r="F154" s="6"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="4"/>
+      <c r="F154" s="3"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
-      <c r="E155" s="7"/>
-      <c r="F155" s="6"/>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="3"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
-      <c r="E156" s="7"/>
-      <c r="F156" s="6"/>
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="4"/>
+      <c r="F156" s="3"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="6"/>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="4"/>
+      <c r="F157" s="3"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="6"/>
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="3"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="6"/>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="4"/>
+      <c r="F159" s="3"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
-      <c r="E160" s="7"/>
-      <c r="F160" s="6"/>
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="3"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
-      <c r="E161" s="7"/>
-      <c r="F161" s="6"/>
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="3"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="6"/>
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="3"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="7"/>
-      <c r="F163" s="6"/>
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="3"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="6"/>
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="4"/>
+      <c r="F164" s="3"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
-      <c r="E165" s="7"/>
-      <c r="F165" s="6"/>
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="3"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="7"/>
-      <c r="F166" s="6"/>
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="3"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="6"/>
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="4"/>
+      <c r="F167" s="3"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="7"/>
-      <c r="F168" s="6"/>
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="4"/>
+      <c r="F168" s="3"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="6"/>
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="4"/>
+      <c r="F169" s="3"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="7"/>
-      <c r="F170" s="6"/>
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="4"/>
+      <c r="F170" s="3"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="7"/>
-      <c r="F171" s="6"/>
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="3"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="7"/>
-      <c r="F172" s="6"/>
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="4"/>
+      <c r="F172" s="3"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="7"/>
-      <c r="F173" s="6"/>
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="4"/>
+      <c r="F173" s="3"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="7"/>
-      <c r="F174" s="6"/>
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="4"/>
+      <c r="F174" s="3"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="6"/>
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="4"/>
+      <c r="F175" s="3"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="7"/>
-      <c r="F176" s="6"/>
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="3"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="7"/>
-      <c r="F177" s="6"/>
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
+      <c r="E177" s="4"/>
+      <c r="F177" s="3"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="6"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
+      <c r="E178" s="4"/>
+      <c r="F178" s="3"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="6"/>
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="3"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="6"/>
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="3"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="6"/>
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="4"/>
+      <c r="F181" s="3"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="7"/>
-      <c r="F182" s="6"/>
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="4"/>
+      <c r="F182" s="3"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="7"/>
-      <c r="F183" s="6"/>
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
+      <c r="E183" s="4"/>
+      <c r="F183" s="3"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="7"/>
-      <c r="F184" s="6"/>
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
+      <c r="E184" s="4"/>
+      <c r="F184" s="3"/>
     </row>
     <row r="185" ht="14.25" customHeight="1"/>
     <row r="186" ht="14.25" customHeight="1"/>
